--- a/business/FlipPulse_Business_Model.xlsx
+++ b/business/FlipPulse_Business_Model.xlsx
@@ -123,10 +123,10 @@
     <xf numFmtId="165" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -577,7 +577,12 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>0.2</v>
+        <v>0</v>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER — temporarily removed / not currently charged. Set e.g. 0.20 to re-enable.</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -586,12 +591,12 @@
           <t>Include performance fee in headline totals? (1=yes, 0=no)</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n">
+      <c r="B8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>Kept OFF by default — it's an illustrative upside, and needs compliance review.</t>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Leave 0 while the fee is on hold; needs compliance review before enabling.</t>
         </is>
       </c>
     </row>
@@ -613,7 +618,7 @@
       <c r="B11" s="6" t="n">
         <v>2000</v>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>Your guess of the typical account size.</t>
         </is>
@@ -628,7 +633,7 @@
       <c r="B12" s="7" t="n">
         <v>0.05</v>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>The bot's real edge is unproven (paper mode by default). Adjust freely.</t>
         </is>
@@ -691,7 +696,7 @@
       <c r="B20" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>Each customer = one always-on bot. ~$3–8/mo of usage each; tune to real bills.</t>
         </is>
@@ -706,7 +711,7 @@
       <c r="B21" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>Free covers unlimited private repos. Team is $4/user if you add staff.</t>
         </is>
@@ -817,10 +822,10 @@
           <t>Purchase in month (1–12)</t>
         </is>
       </c>
-      <c r="B34" s="8" t="n">
+      <c r="B34" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>Only sensible once cumulative profit covers it — see the Summary check.</t>
         </is>
@@ -1824,9 +1829,9 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>* Perf fee is illustrative (needs compliance review) and is OFF in totals unless Inputs!B8 = 1.</t>
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>* Performance fee is a PLACEHOLDER — currently 0% (not charged). Set Inputs!B7 + B8 to re-enable.</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2161,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>PERFORMANCE-FEE UPSIDE  (illustrative, not in totals above)</t>
+          <t>PERFORMANCE-FEE UPSIDE  (PLACEHOLDER — currently 0%, not charged)</t>
         </is>
       </c>
       <c r="B29" s="4" t="n"/>
@@ -2167,7 +2172,7 @@
     <row r="30">
       <c r="A30" s="21" t="inlineStr">
         <is>
-          <t>Annual performance-fee revenue (if it holds)</t>
+          <t>Annual performance-fee revenue (0 while on hold)</t>
         </is>
       </c>
       <c r="B30" s="18">
@@ -2198,9 +2203,9 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>Upside assumes every active customer nets Inputs!B12 per month on Inputs!B11 of capital. Unproven — treat as a ceiling, not a forecast.</t>
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>Performance fee is temporarily removed (Inputs!B7 = 0), so this reads $0. Set a % on the Inputs sheet to model it as an upside — unproven, so treat as a ceiling, not a forecast.</t>
         </is>
       </c>
     </row>
